--- a/diseases/d145/2015-2019.xlsx
+++ b/diseases/d145/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -2049,9 +2046,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -3185,9 +3179,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4321,9 +4312,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5605,9 +5593,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6741,9 +6726,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -7877,9 +7859,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9161,9 +9140,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10297,9 +10273,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11433,9 +11406,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01926867293373831</v>
       </c>
@@ -12717,9 +12687,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13851,9 +13818,6 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
